--- a/Result/profitability/4502.xlsx
+++ b/Result/profitability/4502.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.57</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2387499999999999</v>
+        <v>-0.2299999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>13.47875</v>
+        <v>13.56875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.4</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.29125</v>
+        <v>-0.2849999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>12.25625</v>
+        <v>11.9</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-1.13</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4374999999999999</v>
+        <v>-0.4349999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>10.3825</v>
+        <v>10.465</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-3.58</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8937499999999999</v>
+        <v>-0.79625</v>
       </c>
       <c r="N5" t="n">
-        <v>8.094999999999999</v>
+        <v>8.06875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.13</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.79125</v>
+        <v>-0.7212500000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>6.895</v>
+        <v>7.63625</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.66</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8149999999999999</v>
+        <v>-0.75125</v>
       </c>
       <c r="N7" t="n">
-        <v>4.2175</v>
+        <v>5.766249999999999</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>-0.96</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8825</v>
+        <v>-0.885</v>
       </c>
       <c r="N8" t="n">
-        <v>3.22875</v>
+        <v>2.78875</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>0.21</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9324999999999999</v>
+        <v>-0.9325</v>
       </c>
       <c r="N10" t="n">
         <v>1.055</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4502</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>322</v>
+      </c>
+      <c r="D75" t="n">
+        <v>269</v>
+      </c>
+      <c r="E75" t="n">
+        <v>53</v>
+      </c>
+      <c r="F75" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-0.56%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>6</v>
+      </c>
+      <c r="J75" t="n">
+        <v>4</v>
+      </c>
+      <c r="K75" t="n">
+        <v>5</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.1562499999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>14.86</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.1818181818181819</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-3.52</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1758241758241758</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.7799999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.130434782608696</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.2100000000000009</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.0125673249551167</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
